--- a/uploads/room_mapping.xlsx
+++ b/uploads/room_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\float_working2\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82DF41C-7617-4AF9-823D-5131A3FC02C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A2D6B3-964E-4B83-BC36-647A470F4B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F2E3252-A846-4A0E-8072-090428F4B060}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>S6_CSE_A</t>
   </si>
@@ -47,9 +47,6 @@
     <t>S4_CSE_A</t>
   </si>
   <si>
-    <t>A301</t>
-  </si>
-  <si>
     <t>S4_CSE_B</t>
   </si>
   <si>
@@ -62,12 +59,6 @@
     <t>A302</t>
   </si>
   <si>
-    <t>A201</t>
-  </si>
-  <si>
-    <t>A202</t>
-  </si>
-  <si>
     <t>S6_ME</t>
   </si>
   <si>
@@ -92,48 +83,24 @@
     <t>S4_AI_ML</t>
   </si>
   <si>
-    <t>A501</t>
-  </si>
-  <si>
     <t>A408</t>
   </si>
   <si>
     <t>A306</t>
   </si>
   <si>
-    <t>A204</t>
-  </si>
-  <si>
     <t>A502</t>
   </si>
   <si>
     <t>A504</t>
   </si>
   <si>
-    <t>A303</t>
-  </si>
-  <si>
-    <t>A407</t>
-  </si>
-  <si>
     <t>A205</t>
   </si>
   <si>
-    <t>A505</t>
-  </si>
-  <si>
     <t>A503</t>
   </si>
   <si>
-    <t>A208</t>
-  </si>
-  <si>
-    <t>A601</t>
-  </si>
-  <si>
-    <t>A602</t>
-  </si>
-  <si>
     <t>S6_CE</t>
   </si>
   <si>
@@ -159,6 +126,45 @@
   </si>
   <si>
     <t>S2_ECE</t>
+  </si>
+  <si>
+    <t>A213</t>
+  </si>
+  <si>
+    <t>A214</t>
+  </si>
+  <si>
+    <t>A406</t>
+  </si>
+  <si>
+    <t>A414</t>
+  </si>
+  <si>
+    <t>A409</t>
+  </si>
+  <si>
+    <t>A308</t>
+  </si>
+  <si>
+    <t>A203</t>
+  </si>
+  <si>
+    <t>A309</t>
+  </si>
+  <si>
+    <t>A303A</t>
+  </si>
+  <si>
+    <t>A220</t>
+  </si>
+  <si>
+    <t>A303B</t>
+  </si>
+  <si>
+    <t>A206</t>
+  </si>
+  <si>
+    <t>A305</t>
   </si>
 </sst>
 </file>
@@ -535,13 +541,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -549,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -560,7 +566,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -571,7 +577,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>60</v>
@@ -579,10 +585,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>60</v>
@@ -590,10 +596,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -601,10 +607,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>60</v>
@@ -612,10 +618,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>60</v>
@@ -623,10 +629,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -634,10 +640,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>60</v>
@@ -645,10 +651,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -656,10 +662,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -667,10 +673,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>60</v>
@@ -678,10 +684,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -689,10 +695,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>60</v>
@@ -700,10 +706,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -711,10 +717,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>60</v>
@@ -722,10 +728,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>60</v>
@@ -733,10 +739,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>60</v>
@@ -744,10 +750,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>60</v>
@@ -755,10 +761,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C21">
         <v>60</v>

--- a/uploads/room_mapping.xlsx
+++ b/uploads/room_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A2D6B3-964E-4B83-BC36-647A470F4B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33A4811-A1EC-4ED0-B393-2DCE33D98BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F2E3252-A846-4A0E-8072-090428F4B060}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>S6_CSE_A</t>
   </si>
@@ -165,6 +165,27 @@
   </si>
   <si>
     <t>A305</t>
+  </si>
+  <si>
+    <t>B406</t>
+  </si>
+  <si>
+    <t>A401</t>
+  </si>
+  <si>
+    <t>A513</t>
+  </si>
+  <si>
+    <t>B407</t>
+  </si>
+  <si>
+    <t>B409</t>
+  </si>
+  <si>
+    <t>B405</t>
+  </si>
+  <si>
+    <t>A512</t>
   </si>
 </sst>
 </file>
@@ -536,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3935CA-7760-4391-810A-C3351C5882AD}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -558,7 +579,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -569,7 +590,7 @@
         <v>34</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -580,7 +601,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -591,7 +612,7 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +623,7 @@
         <v>30</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -613,7 +634,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -624,7 +645,7 @@
         <v>35</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -635,7 +656,7 @@
         <v>36</v>
       </c>
       <c r="C9">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -646,7 +667,7 @@
         <v>37</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -657,7 +678,7 @@
         <v>17</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -668,7 +689,7 @@
         <v>38</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -679,7 +700,7 @@
         <v>39</v>
       </c>
       <c r="C13">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -690,7 +711,7 @@
         <v>18</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -701,7 +722,7 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -712,7 +733,7 @@
         <v>19</v>
       </c>
       <c r="C16">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -723,7 +744,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -734,7 +755,7 @@
         <v>40</v>
       </c>
       <c r="C18">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -745,7 +766,7 @@
         <v>41</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -756,7 +777,7 @@
         <v>42</v>
       </c>
       <c r="C20">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -767,7 +788,63 @@
         <v>16</v>
       </c>
       <c r="C21">
-        <v>60</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
